--- a/12630050.xlsx
+++ b/12630050.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF4DB927-E165-465F-8438-A2B2576922D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E4CD05B-330D-495D-A4A5-66B4F9F26436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -236,6 +236,12 @@
   </si>
   <si>
     <t>Feeling satisfied with my work today</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +1158,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="13">
         <v>46274</v>
       </c>
@@ -1378,7 +1384,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="13">
         <v>46279</v>
       </c>
@@ -1654,7 +1660,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="13">
         <v>46285</v>
       </c>
@@ -1838,7 +1844,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="13">
         <v>46289</v>
       </c>
@@ -1886,7 +1892,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="13">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B25" s="14">
         <v>400</v>
@@ -1930,181 +1936,373 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+    <row r="26" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B26" s="14">
+        <v>400</v>
+      </c>
+      <c r="C26" s="14">
+        <v>30</v>
+      </c>
+      <c r="D26" s="14">
+        <v>240</v>
+      </c>
+      <c r="E26" s="14">
+        <v>180</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>60</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B27" s="14">
+        <v>400</v>
+      </c>
+      <c r="C27" s="14">
+        <v>40</v>
+      </c>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>120</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>50</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>710</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B28" s="14">
+        <v>360</v>
+      </c>
+      <c r="C28" s="14">
+        <v>30</v>
+      </c>
+      <c r="D28" s="14">
+        <v>150</v>
+      </c>
+      <c r="E28" s="14">
+        <v>140</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
+        <v>60</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>740</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+        <v>700</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A29" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>40</v>
+      </c>
+      <c r="D29" s="14">
+        <v>180</v>
+      </c>
+      <c r="E29" s="14">
+        <v>180</v>
+      </c>
+      <c r="F29" s="14">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14">
+        <v>40</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B30" s="14">
+        <v>400</v>
+      </c>
+      <c r="C30" s="14">
+        <v>30</v>
+      </c>
+      <c r="D30" s="14">
+        <v>180</v>
+      </c>
+      <c r="E30" s="14">
+        <v>130</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>40</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B31" s="14">
+        <v>400</v>
+      </c>
+      <c r="C31" s="14">
+        <v>50</v>
+      </c>
+      <c r="D31" s="14">
+        <v>220</v>
+      </c>
+      <c r="E31" s="14">
+        <v>200</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>50</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+        <v>520</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A32" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>40</v>
+      </c>
+      <c r="D32" s="14">
+        <v>200</v>
+      </c>
+      <c r="E32" s="14">
+        <v>220</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>60</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+        <v>500</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A33" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B33" s="14">
+        <v>420</v>
+      </c>
+      <c r="C33" s="14">
+        <v>60</v>
+      </c>
+      <c r="D33" s="14">
+        <v>240</v>
+      </c>
+      <c r="E33" s="14">
+        <v>180</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>60</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="13"/>
